--- a/ANILLOS BAMOER BAÑO.xlsx
+++ b/ANILLOS BAMOER BAÑO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3120BF-ECB6-4262-8639-D88771FC81E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0302A3BA-40FB-409F-91A3-017BF3848564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
@@ -75,13 +75,13 @@
     <t>TALLAS</t>
   </si>
   <si>
-    <t>6--7--8</t>
-  </si>
-  <si>
     <t>NUMERO</t>
   </si>
   <si>
     <t>PRECIO</t>
+  </si>
+  <si>
+    <t>Ajustable</t>
   </si>
 </sst>
 </file>
@@ -147,7 +147,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4F4F4"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,6 +294,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95251</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>182563</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1301751</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1036219</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9C0B53A-03F7-96D2-96AD-D3355E5BCF78}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1571626" y="976313"/>
+          <a:ext cx="1206500" cy="853656"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -617,7 +666,7 @@
     </row>
     <row r="3" spans="1:6" ht="18.75">
       <c r="A3" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
@@ -629,7 +678,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>4</v>
@@ -644,13 +693,13 @@
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="9">
-        <v>4.1100000000000003</v>
+        <v>2.39</v>
       </c>
       <c r="E4" s="4">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1"/>
@@ -1398,10 +1447,11 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" display="https://detail.1688.com/offer/1082467502618.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D4" r:id="rId1" display="https://detail.1688.com/offer/1080485035330.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>